--- a/docs/alliance-templates/alliance-brand-topics.xlsx
+++ b/docs/alliance-templates/alliance-brand-topics.xlsx
@@ -7,26 +7,19 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
-    <sheet name="品牌专题" sheetId="2" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName hidden="true" localSheetId="0" name="_xlnm._FilterDatabase">'品牌专题'!$A$2:$D$2</definedName>
+    <definedName hidden="true" localSheetId="0" name="_xlnm._FilterDatabase">'Sheet1'!$A$1:$D$6</definedName>
   </definedNames>
   <calcPr calcId="122211"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
-  <si>
-    <t>填写说明：
-* 必填列。
-主题：文本，选填
-布局：grid（网格） / timeline（时间线） / magazine（杂志），默认为 grid
-描述：文本，选填</t>
-  </si>
-  <si>
-    <t>专题名称 *</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+  <si>
+    <t>专题名称</t>
   </si>
   <si>
     <t>主题</t>
@@ -36,13 +29,67 @@
   </si>
   <si>
     <t>描述</t>
+  </si>
+  <si>
+    <t>2026年产教融合成果展</t>
+  </si>
+  <si>
+    <t>产教融合成果</t>
+  </si>
+  <si>
+    <t>grid</t>
+  </si>
+  <si>
+    <t>集中展示年度产教融合优秀成果与典型案例</t>
+  </si>
+  <si>
+    <t>人工智能人才培养专题</t>
+  </si>
+  <si>
+    <t>人工智能</t>
+  </si>
+  <si>
+    <t>timeline</t>
+  </si>
+  <si>
+    <t>梳理人工智能方向人才培养历程与成果</t>
+  </si>
+  <si>
+    <t>优秀毕业生风采</t>
+  </si>
+  <si>
+    <t>人才品牌</t>
+  </si>
+  <si>
+    <t>展示近三年优秀毕业生代表</t>
+  </si>
+  <si>
+    <t>合作企业巡礼</t>
+  </si>
+  <si>
+    <t>雇主品牌</t>
+  </si>
+  <si>
+    <t>magazine</t>
+  </si>
+  <si>
+    <t>深度介绍核心合作企业品牌</t>
+  </si>
+  <si>
+    <t>技能竞赛荣誉墙</t>
+  </si>
+  <si>
+    <t>竞赛成果</t>
+  </si>
+  <si>
+    <t>展示师生在各级技能竞赛中的获奖成果</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,14 +99,8 @@
     <font>
       <family val="2"/>
       <b val="1"/>
-      <color rgb="FFFFFFFF"/>
+      <color/>
       <sz val="11"/>
-    </font>
-    <font>
-      <family val="2"/>
-      <i val="1"/>
-      <color rgb="FF808080"/>
-      <sz val="10"/>
     </font>
   </fonts>
   <fills count="3">
@@ -71,7 +112,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF4472C4"/>
+        <fgColor rgb="FFCCE5FF"/>
       </patternFill>
     </fill>
   </fills>
@@ -83,34 +124,18 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFD9D9D9"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFD9D9D9"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFD9D9D9"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFD9D9D9"/>
-      </bottom>
-    </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="false">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="true" applyAlignment="false">
       <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
-      <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -377,42 +402,103 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr filterMode="true"/>
   <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col customWidth="true" max="2" min="1" width="28"/>
-    <col customWidth="true" max="3" min="3" width="22"/>
-    <col customWidth="true" max="4" min="4" width="48"/>
+    <col customWidth="true" max="1" min="1" width="28"/>
+    <col customWidth="true" max="2" min="2" width="22"/>
+    <col customWidth="true" max="3" min="3" width="12"/>
+    <col customWidth="true" max="4" min="4" width="50"/>
   </cols>
   <sheetData>
-    <row r="1" ht="96" customHeight="true">
-      <c r="A1" s="3" t="s">
+    <row r="1" ht="24" customHeight="true">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="2" ht="28" customHeight="true">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="1" t="s">
+    <row r="2" ht="20" customHeight="true">
+      <c r="A2" s="2" t="s">
         <v>4</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="true">
+      <c r="A3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="true">
+      <c r="A4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="true">
+      <c r="A5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="true">
+      <c r="A6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="$A$2:$D$2"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
+  <autoFilter ref="$A$1:$D$6"/>
 </worksheet>
 </file>
--- a/docs/alliance-templates/alliance-brand-topics.xlsx
+++ b/docs/alliance-templates/alliance-brand-topics.xlsx
@@ -1,95 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="true" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌专题" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName hidden="true" localSheetId="0" name="_xlnm._FilterDatabase">'Sheet1'!$A$1:$D$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'品牌专题'!$A$2:$D$2</definedName>
   </definedNames>
-  <calcPr calcId="122211"/>
+  <calcPr calcId="122211" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
-  <si>
-    <t>专题名称</t>
-  </si>
-  <si>
-    <t>主题</t>
-  </si>
-  <si>
-    <t>布局</t>
-  </si>
-  <si>
-    <t>描述</t>
-  </si>
-  <si>
-    <t>2026年产教融合成果展</t>
-  </si>
-  <si>
-    <t>产教融合成果</t>
-  </si>
-  <si>
-    <t>grid</t>
-  </si>
-  <si>
-    <t>集中展示年度产教融合优秀成果与典型案例</t>
-  </si>
-  <si>
-    <t>人工智能人才培养专题</t>
-  </si>
-  <si>
-    <t>人工智能</t>
-  </si>
-  <si>
-    <t>timeline</t>
-  </si>
-  <si>
-    <t>梳理人工智能方向人才培养历程与成果</t>
-  </si>
-  <si>
-    <t>优秀毕业生风采</t>
-  </si>
-  <si>
-    <t>人才品牌</t>
-  </si>
-  <si>
-    <t>展示近三年优秀毕业生代表</t>
-  </si>
-  <si>
-    <t>合作企业巡礼</t>
-  </si>
-  <si>
-    <t>雇主品牌</t>
-  </si>
-  <si>
-    <t>magazine</t>
-  </si>
-  <si>
-    <t>深度介绍核心合作企业品牌</t>
-  </si>
-  <si>
-    <t>技能竞赛荣誉墙</t>
-  </si>
-  <si>
-    <t>竞赛成果</t>
-  </si>
-  <si>
-    <t>展示师生在各级技能竞赛中的获奖成果</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -99,13 +28,23 @@
     <font>
       <family val="2"/>
       <b val="1"/>
-      <color/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <color rgb="00666666"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -115,8 +54,20 @@
         <fgColor rgb="FFCCE5FF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+        <bgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -125,24 +76,113 @@
       <diagonal/>
     </border>
     <border/>
+    <border>
+      <left style="thin">
+        <color rgb="00B0B0B0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00B0B0B0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B0B0B0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B0B0B0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+  <cellXfs count="7">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="true" applyAlignment="false">
-      <alignment/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -403,102 +443,171 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="true"/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="28"/>
-    <col customWidth="true" max="2" min="2" width="22"/>
-    <col customWidth="true" max="3" min="3" width="12"/>
-    <col customWidth="true" max="4" min="4" width="50"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="true">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
+    <row r="1" ht="112" customHeight="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>填写说明：
+* 必填列。
+主题：文本，选填
+布局：grid（网格） / timeline（时间线） / magazine（杂志），默认为 grid
+描述：文本，选填</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="n"/>
+      <c r="C1" s="4" t="n"/>
+      <c r="D1" s="4" t="n"/>
     </row>
-    <row r="2" ht="20" customHeight="true">
-      <c r="A2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>7</v>
+    <row r="2" ht="28" customHeight="1">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>专题名称 *</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>主题</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>布局</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>描述</t>
+        </is>
       </c>
     </row>
-    <row r="3" ht="20" customHeight="true">
-      <c r="A3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>11</v>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>2026年产教融合成果展</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>产教融合成果</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>grid</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>集中展示年度产教融合优秀成果与典型案例</t>
+        </is>
       </c>
     </row>
-    <row r="4" ht="20" customHeight="true">
-      <c r="A4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>14</v>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>人工智能人才培养专题</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>人工智能</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>timeline</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>梳理人工智能方向人才培养历程与成果</t>
+        </is>
       </c>
     </row>
-    <row r="5" ht="20" customHeight="true">
-      <c r="A5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>18</v>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>优秀毕业生风采</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>人才品牌</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>grid</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>展示近三年优秀毕业生代表</t>
+        </is>
       </c>
     </row>
-    <row r="6" ht="20" customHeight="true">
-      <c r="A6" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>21</v>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>合作企业巡礼</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>雇主品牌</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>magazine</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>深度介绍核心合作企业品牌</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>技能竞赛荣誉墙</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>竞赛成果</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>grid</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>展示师生在各级技能竞赛中的获奖成果</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="$A$1:$D$6"/>
+  <autoFilter ref="A2:D2"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/alliance-templates/alliance-brand-topics.xlsx
+++ b/docs/alliance-templates/alliance-brand-topics.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌专题" sheetId="1" state="visible" r:id="rId1"/>
@@ -67,7 +67,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -90,11 +90,55 @@
         <color rgb="00B0B0B0"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B0B0B0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B0B0B0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B0B0B0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B0B0B0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B0B0B0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B0B0B0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B0B0B0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B0B0B0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -110,6 +154,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -467,9 +513,9 @@
 描述：文本，选填</t>
         </is>
       </c>
-      <c r="B1" s="4" t="n"/>
-      <c r="C1" s="4" t="n"/>
-      <c r="D1" s="4" t="n"/>
+      <c r="B1" s="7" t="n"/>
+      <c r="C1" s="7" t="n"/>
+      <c r="D1" s="8" t="n"/>
     </row>
     <row r="2" ht="28" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
@@ -506,7 +552,7 @@
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>grid</t>
+          <t>网格</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
@@ -528,7 +574,7 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>timeline</t>
+          <t>时间线</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
@@ -550,7 +596,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>grid</t>
+          <t>网格</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
@@ -572,7 +618,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>magazine</t>
+          <t>杂志</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -594,7 +640,7 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>grid</t>
+          <t>网格</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
